--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalven 225 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 450 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -819,7 +819,7 @@
         <v>136370093</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,32 +955,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136352733</v>
+        <v>136390574</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -988,28 +988,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521191</v>
+        <v>521217</v>
       </c>
       <c r="R4" t="n">
-        <v>6637198</v>
+        <v>6637375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1044,17 +1039,13 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hackmärken i tallåga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1065,22 +1056,30 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>1 substratenheter # Branch on living tree # död kvist # Picea abies # grovt träd</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1097,70 +1096,65 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352733</t>
+          <t>https://artportalen.se/Sighting/136390574</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136369839</v>
+        <v>136390613</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521218</v>
+        <v>521227</v>
       </c>
       <c r="R5" t="n">
-        <v>6637248</v>
+        <v>6637369</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1194,7 +1188,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hackmärken i talltorraka</t>
+          <t>minst tre stora bålar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,6 +1197,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1213,22 +1208,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+          <t>Dead branch  # död gren på grovt levande träd # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1245,59 +1240,62 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369839</t>
+          <t>https://artportalen.se/Sighting/136390613</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136370107</v>
+        <v>136390682</v>
       </c>
       <c r="B6" t="n">
-        <v>106330</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221154</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521195</v>
+        <v>521216</v>
       </c>
       <c r="R6" t="n">
-        <v>6637298</v>
+        <v>6637370</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1347,6 +1345,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # död kvist på grovt levande träd # Picea abies # grovt träd</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1361,38 +1384,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370107</t>
+          <t>https://artportalen.se/Sighting/136390682</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136369811</v>
+        <v>136391062</v>
       </c>
       <c r="B7" t="n">
-        <v>79054</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228595</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulvit renlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia arbuscula</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wallr.) Flot.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1401,14 +1424,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521218</v>
+        <v>521225</v>
       </c>
       <c r="R7" t="n">
-        <v>6637248</v>
+        <v>6637365</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1458,6 +1481,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>klent träd</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torrgran # Picea abies # klent träd</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1472,54 +1520,62 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369811</t>
+          <t>https://artportalen.se/Sighting/136391062</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136369816</v>
+        <v>136391089</v>
       </c>
       <c r="B8" t="n">
-        <v>79131</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228654</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521218</v>
+        <v>521228</v>
       </c>
       <c r="R8" t="n">
-        <v>6637248</v>
+        <v>6637353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1569,6 +1625,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1583,54 +1664,62 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369816</t>
+          <t>https://artportalen.se/Sighting/136391089</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136369808</v>
+        <v>136391098</v>
       </c>
       <c r="B9" t="n">
-        <v>79138</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228659</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521218</v>
+        <v>521238</v>
       </c>
       <c r="R9" t="n">
-        <v>6637248</v>
+        <v>6637348</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,6 +1769,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1693,6 +1807,2186 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391098</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136391109</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>521242</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6637354</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391109</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136391120</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>521246</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6637352</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En meterlång bål!</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391120</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136391129</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>521256</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6637342</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>minst två bålar</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391129</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136391139</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>521237</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6637345</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>levande klent träd</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande klent träd</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391139</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136391147</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>521235</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6637338</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391147</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136391158</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>521239</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6637335</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391158</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136391189</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>521231</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6637340</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>en bål på klen torrkvist på en klen liten gran och en bål på död gren på grov levande gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391189</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136391199</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>521242</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6637326</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Dead branch  # torrkvist # Picea abies # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391199</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136391288</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kalven 200 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>521285</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6637307</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>klen torrgran</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Dead branch  # Picea abies # klen torrgran</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391288</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136352733</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>521191</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6637198</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska hackmärken i tallåga</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136352733</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136369839</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hackmärken i talltorraka</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369839</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136391215</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>521254</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6637318</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska hackmärken i tallåga</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391215</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136370107</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106343</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>521195</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6637298</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370107</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136369811</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79060</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369811</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136369816</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79137</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369816</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136369808</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79144</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136369808</t>
         </is>
@@ -1708,6 +4002,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,56 +816,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136370093</v>
+        <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521195</v>
+        <v>521325</v>
       </c>
       <c r="R3" t="n">
-        <v>6637298</v>
+        <v>6637266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,22 +914,25 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # och på stammen # Picea abies</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov, murken låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,38 +949,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370093</t>
+          <t>https://artportalen.se/Sighting/136405698</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136390574</v>
+        <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -988,23 +988,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521217</v>
+        <v>521323</v>
       </c>
       <c r="R4" t="n">
-        <v>6637375</v>
+        <v>6637251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1039,6 +1040,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1056,30 +1062,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # Branch on living tree # död kvist # Picea abies # grovt träd</t>
+          <t>Horizontal, dead with ground contact # murken låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,62 +1094,59 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136390574</t>
+          <t>https://artportalen.se/Sighting/136418092</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136390613</v>
+        <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521227</v>
+        <v>521332</v>
       </c>
       <c r="R5" t="n">
-        <v>6637369</v>
+        <v>6637239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>minst tre stora bålar</t>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1208,22 +1203,25 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Dead branch  # död gren på grovt levande träd # Picea abies</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1240,62 +1238,59 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136390613</t>
+          <t>https://artportalen.se/Sighting/136418147</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136390682</v>
+        <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521216</v>
+        <v>521318</v>
       </c>
       <c r="R6" t="n">
-        <v>6637370</v>
+        <v>6637218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1347,27 +1342,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>grovt träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Dead branch  # död kvist på grovt levande träd # Picea abies # grovt träd</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,54 +1374,59 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136390682</t>
+          <t>https://artportalen.se/Sighting/136418154</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136391062</v>
+        <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521225</v>
+        <v>521306</v>
       </c>
       <c r="R7" t="n">
-        <v>6637365</v>
+        <v>6637222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1466,6 +1461,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1483,27 +1483,25 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>klent träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # torrgran # Picea abies # klent träd</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1520,62 +1518,59 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391062</t>
+          <t>https://artportalen.se/Sighting/136418162</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136391089</v>
+        <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521228</v>
+        <v>521305</v>
       </c>
       <c r="R8" t="n">
-        <v>6637353</v>
+        <v>6637228</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1610,6 +1605,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1627,27 +1627,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # levande träd</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1664,62 +1659,63 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391089</t>
+          <t>https://artportalen.se/Sighting/136418193</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136391098</v>
+        <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521238</v>
+        <v>521294</v>
       </c>
       <c r="R9" t="n">
-        <v>6637348</v>
+        <v>6637211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1771,27 +1767,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # levande träd</t>
+          <t>Horizontal, dead with ground contact # murken grov låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1808,62 +1799,59 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391098</t>
+          <t>https://artportalen.se/Sighting/136418203</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136391109</v>
+        <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521242</v>
+        <v>521297</v>
       </c>
       <c r="R10" t="n">
-        <v>6637354</v>
+        <v>6637173</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1915,27 +1903,25 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # levande träd</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # murken låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1952,62 +1938,59 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391109</t>
+          <t>https://artportalen.se/Sighting/136418281</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136391120</v>
+        <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521246</v>
+        <v>521295</v>
       </c>
       <c r="R11" t="n">
-        <v>6637352</v>
+        <v>6637160</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2042,11 +2025,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En meterlång bål!</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2062,29 +2040,22 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>levande träd</t>
+          <t>barrträd</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # levande träd</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # klen låga # barrträd</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2101,62 +2072,59 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391120</t>
+          <t>https://artportalen.se/Sighting/136418303</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136391129</v>
+        <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521256</v>
+        <v>521292</v>
       </c>
       <c r="R12" t="n">
-        <v>6637342</v>
+        <v>6637147</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2191,11 +2159,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>minst två bålar</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2211,29 +2174,17 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>levande träd</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # levande träd</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov låga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2250,62 +2201,59 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391129</t>
+          <t>https://artportalen.se/Sighting/136418369</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136391139</v>
+        <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521237</v>
+        <v>521291</v>
       </c>
       <c r="R13" t="n">
-        <v>6637345</v>
+        <v>6637116</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2365,19 +2313,17 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>levande klent träd</t>
-        </is>
-      </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # levande klent träd</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # klen murken låga # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2394,54 +2340,59 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391139</t>
+          <t>https://artportalen.se/Sighting/136418381</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136391147</v>
+        <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521235</v>
+        <v>521208</v>
       </c>
       <c r="R14" t="n">
-        <v>6637338</v>
+        <v>6637184</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2476,6 +2427,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2493,22 +2449,25 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2525,62 +2484,59 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391147</t>
+          <t>https://artportalen.se/Sighting/136418477</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136391158</v>
+        <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>79460</v>
+        <v>97564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521239</v>
+        <v>521202</v>
       </c>
       <c r="R15" t="n">
-        <v>6637335</v>
+        <v>6637212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2615,6 +2571,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2632,22 +2593,25 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2664,13 +2628,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391158</t>
+          <t>https://artportalen.se/Sighting/136418555</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136391189</v>
+        <v>136370093</v>
       </c>
       <c r="B16" t="n">
         <v>79460</v>
@@ -2700,7 +2664,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2712,14 +2676,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521231</v>
+        <v>521195</v>
       </c>
       <c r="R16" t="n">
-        <v>6637340</v>
+        <v>6637298</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2754,11 +2718,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>en bål på klen torrkvist på en klen liten gran och en bål på död gren på grov levande gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2786,12 +2745,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # och på stammen # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2808,13 +2767,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391189</t>
+          <t>https://artportalen.se/Sighting/136370093</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136391199</v>
+        <v>136390574</v>
       </c>
       <c r="B17" t="n">
         <v>79460</v>
@@ -2856,14 +2815,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521242</v>
+        <v>521217</v>
       </c>
       <c r="R17" t="n">
-        <v>6637326</v>
+        <v>6637375</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2930,12 +2889,15 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Död gren</t>
-        </is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Dead branch  # torrkvist # Picea abies # grovt träd</t>
+          <t>1 substratenheter # Branch on living tree # död kvist # Picea abies # grovt träd</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2952,13 +2914,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391199</t>
+          <t>https://artportalen.se/Sighting/136390574</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136391288</v>
+        <v>136390613</v>
       </c>
       <c r="B18" t="n">
         <v>79460</v>
@@ -2988,7 +2950,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3000,14 +2962,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalven 200 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521285</v>
+        <v>521227</v>
       </c>
       <c r="R18" t="n">
-        <v>6637307</v>
+        <v>6637369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3042,6 +3004,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>minst tre stora bålar</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -3067,22 +3034,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>klen torrgran</t>
-        </is>
-      </c>
       <c r="AM18" t="inlineStr">
         <is>
           <t>Död gren</t>
         </is>
       </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # Dead branch  # Picea abies # klen torrgran</t>
+          <t>Dead branch  # död gren på grovt levande träd # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3099,38 +3058,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391288</t>
+          <t>https://artportalen.se/Sighting/136390613</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136352733</v>
+        <v>136390682</v>
       </c>
       <c r="B19" t="n">
-        <v>57990</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3138,28 +3097,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven V om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521191</v>
+        <v>521216</v>
       </c>
       <c r="R19" t="n">
-        <v>6637198</v>
+        <v>6637370</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3194,17 +3148,13 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska hackmärken i tallåga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3215,22 +3165,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Dead branch  # död kvist på grovt levande träd # Picea abies # grovt träd</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3247,70 +3202,57 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352733</t>
+          <t>https://artportalen.se/Sighting/136390682</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136369839</v>
+        <v>136391062</v>
       </c>
       <c r="B20" t="n">
-        <v>57990</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521218</v>
+        <v>521225</v>
       </c>
       <c r="R20" t="n">
-        <v>6637248</v>
+        <v>6637365</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3342,17 +3284,13 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hackmärken i talltorraka</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3363,12 +3301,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>klent träd</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -3378,7 +3321,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # torrgran # Picea abies # klent träd</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3395,63 +3338,62 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369839</t>
+          <t>https://artportalen.se/Sighting/136391062</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136391215</v>
+        <v>136391089</v>
       </c>
       <c r="B21" t="n">
-        <v>57990</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521254</v>
+        <v>521228</v>
       </c>
       <c r="R21" t="n">
-        <v>6637318</v>
+        <v>6637353</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3486,17 +3428,13 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska hackmärken i tallåga</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3507,22 +3445,27 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>levande träd</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies # levande träd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3539,59 +3482,62 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136391215</t>
+          <t>https://artportalen.se/Sighting/136391089</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136370107</v>
+        <v>136391098</v>
       </c>
       <c r="B22" t="n">
-        <v>106343</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221154</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521195</v>
+        <v>521238</v>
       </c>
       <c r="R22" t="n">
-        <v>6637298</v>
+        <v>6637348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3641,6 +3587,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -3655,54 +3626,62 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370107</t>
+          <t>https://artportalen.se/Sighting/136391098</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136369811</v>
+        <v>136391109</v>
       </c>
       <c r="B23" t="n">
-        <v>79060</v>
+        <v>79460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228595</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulvit renlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia arbuscula</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wallr.) Flot.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521218</v>
+        <v>521242</v>
       </c>
       <c r="R23" t="n">
-        <v>6637248</v>
+        <v>6637354</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3752,6 +3731,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3766,54 +3770,62 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369811</t>
+          <t>https://artportalen.se/Sighting/136391109</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136369816</v>
+        <v>136391120</v>
       </c>
       <c r="B24" t="n">
-        <v>79137</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228654</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521218</v>
+        <v>521246</v>
       </c>
       <c r="R24" t="n">
-        <v>6637248</v>
+        <v>6637352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3848,6 +3860,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En meterlång bål!</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3863,6 +3880,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
@@ -3877,54 +3919,62 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369816</t>
+          <t>https://artportalen.se/Sighting/136391120</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136369808</v>
+        <v>136391129</v>
       </c>
       <c r="B25" t="n">
-        <v>79144</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228659</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521218</v>
+        <v>521256</v>
       </c>
       <c r="R25" t="n">
-        <v>6637248</v>
+        <v>6637342</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3959,6 +4009,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>minst två bålar</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3974,6 +4029,31 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>levande träd</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande träd</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3987,6 +4067,3059 @@
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391129</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136391139</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>521237</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6637345</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>levande klent träd</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # levande klent träd</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391139</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136391147</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>521235</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6637338</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391147</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136391158</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>521239</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6637335</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391158</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136391189</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>521231</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6637340</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>en bål på klen torrkvist på en klen liten gran och en bål på död gren på grov levande gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391189</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136391199</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>521242</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6637326</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead branch  # torrkvist # Picea abies # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391199</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136391288</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kalven 200 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>521285</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6637307</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>klen torrgran</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Dead branch  # Picea abies # klen torrgran</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391288</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136405636</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>521301</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6637309</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Dead branch  # torrkvist # Picea abies # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136405636</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136405650</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>521311</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6637302</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På döda och levande grenar på fyra granar i en samlad trädgrupp.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>fyra träd i tät grupp</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # både döda och levande grenar # Picea abies # fyra träd i tät grupp</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136405650</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136405663</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>521327</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6637289</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136405663</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136418408</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>521258</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6637130</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Branch on living tree # torrkvist # Picea abies # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136418408</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136418424</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>521250</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6637130</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Branch on living tree # torrkvist # Picea abies # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136418424</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136418441</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>521222</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6637167</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Branch on living tree # torrkvist # Picea abies # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136418441</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136418448</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>521217</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6637164</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Branch on living tree # torrkvistar # Picea abies # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136418448</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136418460</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79460</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>521226</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6637168</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Branch on living tree # torrkvist # Picea abies # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136418460</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136352733</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>521191</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6637198</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska hackmärken i tallåga</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136352733</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136369839</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>hackmärken i talltorraka</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369839</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136391215</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kalven VSV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>521254</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6637318</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>färska hackmärken i tallåga</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136391215</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136405709</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57990</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kalven SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>521325</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6637266</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>hackmärken i murken tallåga</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # grov, murken låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136405709</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136370107</v>
+      </c>
+      <c r="B44" t="n">
+        <v>106343</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>521195</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6637298</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370107</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136369811</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79060</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369811</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136369816</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79137</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369816</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136369808</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79144</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136369808</t>
         </is>
@@ -4018,6 +7151,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>136370107</v>
       </c>
       <c r="B44" t="n">
-        <v>106343</v>
+        <v>106344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>136370093</v>
       </c>
       <c r="B16" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>136390574</v>
       </c>
       <c r="B17" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136390613</v>
       </c>
       <c r="B18" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>136390682</v>
       </c>
       <c r="B19" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>136391062</v>
       </c>
       <c r="B20" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>136391089</v>
       </c>
       <c r="B21" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136391098</v>
       </c>
       <c r="B22" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136391109</v>
       </c>
       <c r="B23" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136391120</v>
       </c>
       <c r="B24" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>136391129</v>
       </c>
       <c r="B25" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136391139</v>
       </c>
       <c r="B26" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>136391147</v>
       </c>
       <c r="B27" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136391158</v>
       </c>
       <c r="B28" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>136391189</v>
       </c>
       <c r="B29" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136391199</v>
       </c>
       <c r="B30" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136391288</v>
       </c>
       <c r="B31" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136405636</v>
       </c>
       <c r="B32" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>136405650</v>
       </c>
       <c r="B33" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136405663</v>
       </c>
       <c r="B34" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>136418408</v>
       </c>
       <c r="B35" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>136418424</v>
       </c>
       <c r="B36" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136418441</v>
       </c>
       <c r="B37" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>136418448</v>
       </c>
       <c r="B38" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>136418460</v>
       </c>
       <c r="B39" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>136352733</v>
       </c>
       <c r="B40" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>136369839</v>
       </c>
       <c r="B41" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>136391215</v>
       </c>
       <c r="B42" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>136405709</v>
       </c>
       <c r="B43" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>136370107</v>
       </c>
       <c r="B44" t="n">
-        <v>106344</v>
+        <v>106357</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>136369811</v>
       </c>
       <c r="B45" t="n">
-        <v>79060</v>
+        <v>79073</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>136369816</v>
       </c>
       <c r="B46" t="n">
-        <v>79137</v>
+        <v>79150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>136369808</v>
       </c>
       <c r="B47" t="n">
-        <v>79144</v>
+        <v>79157</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 35177-2026 artfynd.xlsx
+++ b/artfynd/A 35177-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136405698</v>
       </c>
       <c r="B3" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>136418092</v>
       </c>
       <c r="B4" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136418147</v>
       </c>
       <c r="B5" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136418154</v>
       </c>
       <c r="B6" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>136418162</v>
       </c>
       <c r="B7" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>136418193</v>
       </c>
       <c r="B8" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136418203</v>
       </c>
       <c r="B9" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136418281</v>
       </c>
       <c r="B10" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>136418303</v>
       </c>
       <c r="B11" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>136418369</v>
       </c>
       <c r="B12" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136418381</v>
       </c>
       <c r="B13" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136418477</v>
       </c>
       <c r="B14" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136418555</v>
       </c>
       <c r="B15" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>136370093</v>
       </c>
       <c r="B16" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>136390574</v>
       </c>
       <c r="B17" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136390613</v>
       </c>
       <c r="B18" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>136390682</v>
       </c>
       <c r="B19" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>136391062</v>
       </c>
       <c r="B20" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>136391089</v>
       </c>
       <c r="B21" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136391098</v>
       </c>
       <c r="B22" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136391109</v>
       </c>
       <c r="B23" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>136391120</v>
       </c>
       <c r="B24" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>136391129</v>
       </c>
       <c r="B25" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>136391139</v>
       </c>
       <c r="B26" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>136391147</v>
       </c>
       <c r="B27" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>136391158</v>
       </c>
       <c r="B28" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>136391189</v>
       </c>
       <c r="B29" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136391199</v>
       </c>
       <c r="B30" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136391288</v>
       </c>
       <c r="B31" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>136405636</v>
       </c>
       <c r="B32" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>136405650</v>
       </c>
       <c r="B33" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136405663</v>
       </c>
       <c r="B34" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>136418408</v>
       </c>
       <c r="B35" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>136418424</v>
       </c>
       <c r="B36" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136418441</v>
       </c>
       <c r="B37" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>136418448</v>
       </c>
       <c r="B38" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>136418460</v>
       </c>
       <c r="B39" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>136370107</v>
       </c>
       <c r="B44" t="n">
-        <v>106357</v>
+        <v>106358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>136369811</v>
       </c>
       <c r="B45" t="n">
-        <v>79073</v>
+        <v>79074</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>136369816</v>
       </c>
       <c r="B46" t="n">
-        <v>79150</v>
+        <v>79151</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>136369808</v>
       </c>
       <c r="B47" t="n">
-        <v>79157</v>
+        <v>79158</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
